--- a/release/v2026.4.0/CodeSystem-mii-qst-pro-eortc-qlq-c30_eortc-qlq-c30-cs.xlsx
+++ b/release/v2026.4.0/CodeSystem-mii-qst-pro-eortc-qlq-c30_eortc-qlq-c30-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.4.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/release/v2026.4.0/CodeSystem-mii-qst-pro-eortc-qlq-c30_eortc-qlq-c30-cs.xlsx
+++ b/release/v2026.4.0/CodeSystem-mii-qst-pro-eortc-qlq-c30_eortc-qlq-c30-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.0</t>
+    <t>2026.4.1</t>
   </si>
   <si>
     <t>Name</t>
